--- a/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/pregenereated_results/s2/att_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ATT_MSM" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Covariate_Balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weight_Diagnostics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ATT_MSM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Propensity_Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,13 +480,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.011</v>
+        <v>-0.019</v>
       </c>
       <c r="D2" t="n">
         <v>-0.002</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.043</v>
+        <v>-0.037</v>
       </c>
       <c r="D3" t="n">
         <v>0.003</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03999999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -525,7 +525,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -534,13 +534,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.044</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>0.042</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -552,22 +552,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>binary</t>
+          <t>continuous</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.097</v>
+        <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.003</v>
+        <v>0.001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.094</v>
+        <v>0.045</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -579,22 +579,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>categorical</t>
+          <t>binary</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.027</v>
+        <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>0.025</v>
+        <v>0.094</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.043</v>
+        <v>-0.024</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.042</v>
+        <v>0.022</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.02</v>
+        <v>0.046</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>-0.001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02</v>
+        <v>0.045</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.081</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.078</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.038</v>
+        <v>-0.074</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.037</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.024</v>
+        <v>0.033</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.008</v>
+        <v>0.023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E12" t="n">
-        <v>0.007</v>
+        <v>0.019</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.045</v>
+        <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.008</v>
+        <v>0.001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.037</v>
+        <v>0.006</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="D14" t="n">
-        <v>0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.029</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.005</v>
+        <v>0.007</v>
       </c>
       <c r="E15" t="n">
-        <v>0.024</v>
+        <v>-0.002</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.01</v>
+        <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.008</v>
+        <v>0.028</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0</v>
+        <v>-0.014</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.004</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.002</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.075</v>
+        <v>-0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.074</v>
+        <v>0.006</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.019</v>
+        <v>0.077</v>
       </c>
       <c r="D20" t="n">
         <v>-0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.018</v>
+        <v>0.076</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.109</v>
+        <v>-0.019</v>
       </c>
       <c r="D21" t="n">
-        <v>0.003</v>
+        <v>-0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.106</v>
+        <v>0.019</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.19</v>
+        <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.006</v>
+        <v>0.003</v>
       </c>
       <c r="E22" t="n">
-        <v>0.184</v>
+        <v>0.11</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.146</v>
+        <v>0.197</v>
       </c>
       <c r="D23" t="n">
-        <v>0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="E23" t="n">
-        <v>0.143</v>
+        <v>0.191</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.051</v>
+        <v>-0.143</v>
       </c>
       <c r="D24" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="E24" t="n">
-        <v>0.045</v>
+        <v>0.14</v>
       </c>
       <c r="F24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.118</v>
+        <v>-0.054</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.003</v>
+        <v>0.006</v>
       </c>
       <c r="E25" t="n">
-        <v>0.115</v>
+        <v>0.048</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.218</v>
+        <v>-0.128</v>
       </c>
       <c r="D26" t="n">
         <v>-0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.216</v>
+        <v>0.126</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Exceeds</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.254</v>
+        <v>0.227</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="E27" t="n">
-        <v>0.252</v>
+        <v>0.225</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Below</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.328</v>
+        <v>0.392</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.001</v>
+        <v>-0.008</v>
       </c>
       <c r="E28" t="n">
-        <v>0.327</v>
+        <v>0.384</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.436</v>
+        <v>-0.401</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.008</v>
+        <v>0.005</v>
       </c>
       <c r="E29" t="n">
-        <v>0.428</v>
+        <v>0.396</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.06</v>
+        <v>0.107</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="E30" t="n">
-        <v>0.055</v>
+        <v>0.104</v>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.108</v>
+        <v>-0.041</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.003</v>
+        <v>-0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.105</v>
+        <v>0.041</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.046</v>
+        <v>-0.066</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="E32" t="n">
-        <v>0.045</v>
+        <v>0.059</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,45 +1317,18 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-0.068</v>
+        <v>0.022</v>
       </c>
       <c r="D33" t="n">
-        <v>0.006</v>
+        <v>-0.004</v>
       </c>
       <c r="E33" t="n">
-        <v>0.06200000000000001</v>
+        <v>0.018</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>region_North_America</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>categorical</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1412,16 +1385,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9000</v>
+        <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>541.114156846371</v>
+        <v>554.8319074166568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0570484345693796</v>
+        <v>0.07201588164977409</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2255693013305237</v>
+        <v>0.2496221955703657</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1444,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.068045347517065</v>
+        <v>2.036602236209996</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3463193797776236</v>
+        <v>0.3595551986980526</v>
       </c>
       <c r="D2" t="n">
-        <v>1.389271836004674</v>
+        <v>1.33188699630767</v>
       </c>
       <c r="E2" t="n">
-        <v>2.746818859029457</v>
+        <v>2.741317476112322</v>
       </c>
       <c r="F2" t="n">
-        <v>2.35085510820478e-09</v>
+        <v>1.476888557167581e-08</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.06106215274549592</v>
+        <v>-0.06313566390614948</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07213649219284309</v>
+        <v>0.06889171256433488</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2024470794145232</v>
+        <v>-0.1981609393655314</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08032277392353132</v>
+        <v>0.07188961155323241</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3972846025272195</v>
+        <v>0.3594320324412411</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1397510209367279</v>
+        <v>-0.1420900222427463</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1685780973771287</v>
+        <v>0.1674834691504836</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4701580203781864</v>
+        <v>-0.4703515897835194</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1906559785047305</v>
+        <v>0.1861715452980268</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4071051516960914</v>
+        <v>0.3962250586520983</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1108721669664168</v>
+        <v>0.1123402147235629</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1325411668481562</v>
+        <v>0.1386455160915384</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1489037465248835</v>
+        <v>-0.1594000034338209</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3706480804577171</v>
+        <v>0.3840804328809467</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4028673937427625</v>
+        <v>0.4177853765636296</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2511808211872781</v>
+        <v>0.261615745957696</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1485346199827449</v>
+        <v>0.1491654091054351</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03994168443624535</v>
+        <v>-0.03074308362813982</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5423033268108015</v>
+        <v>0.5539745755435319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0908255151651834</v>
+        <v>0.07945392276127186</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1616,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2239529717126706</v>
+        <v>0.2268721888728757</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1313493401367616</v>
+        <v>0.1322971139673635</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.03348700434848356</v>
+        <v>-0.03242538976174775</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4813929477738249</v>
+        <v>0.4861697675074991</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08819109226545449</v>
+        <v>0.08636928988307624</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2856373533763467</v>
+        <v>0.2700551131784785</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1513332726955047</v>
+        <v>0.1556352113937795</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01097041076942129</v>
+        <v>-0.03498429587960727</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5822451175221146</v>
+        <v>0.5750945222365642</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05909683476621606</v>
+        <v>0.08270891977837894</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1666,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04063507248864447</v>
+        <v>0.05428434711664003</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1230762388391048</v>
+        <v>0.1256761579998879</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2005899229886507</v>
+        <v>-0.1920363962785057</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2818600679659397</v>
+        <v>0.3006050905117857</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7412777094751978</v>
+        <v>0.6657862511070213</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2773232484384246</v>
+        <v>0.2497052052682605</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1826628023502551</v>
+        <v>0.1813103926938767</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0806892654832338</v>
+        <v>-0.1056566344345521</v>
       </c>
       <c r="E10" t="n">
-        <v>0.635335762360083</v>
+        <v>0.6050670449710731</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1289576660431151</v>
+        <v>0.1684426953271448</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0527995908396489</v>
+        <v>-0.05406182499411169</v>
       </c>
       <c r="C11" t="n">
-        <v>0.207699652745158</v>
+        <v>0.2032970913516041</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4598834298216344</v>
+        <v>-0.452516802205005</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3542842481423366</v>
+        <v>0.3443931522167817</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7993323505270289</v>
+        <v>0.7902967967088366</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2016923055741308</v>
+        <v>0.1958077105120102</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1512057636267634</v>
+        <v>0.1454915101622126</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.09466554538920188</v>
+        <v>-0.08935040946226977</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4980501565374634</v>
+        <v>0.4809658304862902</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1822389348572969</v>
+        <v>0.1783554160232425</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2571340913317983</v>
+        <v>0.2559736583242179</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1762449215029054</v>
+        <v>0.1734212677168902</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.08829960727198527</v>
+        <v>-0.08392578055416561</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6025677899355818</v>
+        <v>0.5958730972026014</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1445764287171156</v>
+        <v>0.1399379060136729</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2648173615508135</v>
+        <v>0.2621085393999598</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1666690309010773</v>
+        <v>0.16131856534169</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.06184793635349145</v>
+        <v>-0.05407003870742388</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5914826594551184</v>
+        <v>0.5782871175073435</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1120871191762612</v>
+        <v>0.104207646009069</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1187279536604203</v>
+        <v>0.121769811359689</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1768196755302422</v>
+        <v>0.1773010282590528</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2278322421369128</v>
+        <v>-0.2257338184499728</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4652881494577534</v>
+        <v>0.4692734411693508</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5019253205178047</v>
+        <v>0.4922106710207459</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0914252212951203</v>
+        <v>-0.09452849173092565</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1822149658791681</v>
+        <v>0.1774418821294867</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4485599918624846</v>
+        <v>-0.442308190053721</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2657095492722439</v>
+        <v>0.2532512065918697</v>
       </c>
       <c r="F16" t="n">
-        <v>0.615847781452552</v>
+        <v>0.5942209726114963</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.2069280373241203</v>
+        <v>0.1837143702306887</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1718680033842656</v>
+        <v>0.1637040102408049</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1299270594038484</v>
+        <v>-0.1371395939660652</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5437831340520889</v>
+        <v>0.5045683344274425</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2285919145717531</v>
+        <v>0.2617625340704764</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.08212388380145137</v>
+        <v>-0.06981748387247652</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2029805623264877</v>
+        <v>0.1930840620841167</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4799584755230549</v>
+        <v>-0.4482552915460412</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3157107079201522</v>
+        <v>0.3086203238010881</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6857789897055764</v>
+        <v>0.7176575952681559</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.198867001642657</v>
+        <v>0.1969655303245181</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1830167962734066</v>
+        <v>0.1779209025639866</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1598393276191244</v>
+        <v>-0.1517530307977557</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5575733309044384</v>
+        <v>0.545684091446792</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2772113280849852</v>
+        <v>0.2682766969715202</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1941,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1507097650813221</v>
+        <v>0.1322032620606822</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1763026477405054</v>
+        <v>0.1728217080449768</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1948370748691204</v>
+        <v>-0.2065210614541684</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4962566050317645</v>
+        <v>0.4709275855755328</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3926422126001839</v>
+        <v>0.4442899600438306</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.130969647625536</v>
+        <v>0.141198931221375</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1567581100713807</v>
+        <v>0.1536032454395486</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1762706023989356</v>
+        <v>-0.1598578977486066</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4382098976500076</v>
+        <v>0.4422557601913565</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4034425419470397</v>
+        <v>0.3579677249885992</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.02319130177399187</v>
+        <v>-0.03228862083243213</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1734877082589109</v>
+        <v>0.1700096908231716</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3632209617218493</v>
+        <v>-0.3655014918686382</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3168383581738656</v>
+        <v>0.300924250203774</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8936580598089039</v>
+        <v>0.8493700668133817</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2277502313160918</v>
+        <v>0.2528578615211169</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1704598716724123</v>
+        <v>0.1707882512439054</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1063449779711557</v>
+        <v>-0.08188095989951566</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5618454406033393</v>
+        <v>0.5875966829417496</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1815188968844078</v>
+        <v>0.1387307179459414</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2037,23 +2010,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Exceeds[T.True]</t>
+          <t>performance_rating_Far_Exceeds[T.True]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.02753301441521003</v>
+        <v>0.1009814874983657</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06481647246901312</v>
+        <v>0.1174236802772657</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09950493722898765</v>
+        <v>-0.1291646967772213</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1545709660594077</v>
+        <v>0.3311276717739527</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6709939852767683</v>
+        <v>0.3898025510379953</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2062,23 +2035,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Below[T.True]</t>
+          <t>performance_rating_Meets[T.True]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.04322691575966257</v>
+        <v>0.00433005390115218</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0454703100996182</v>
+        <v>0.08182631997408571</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1323470859207821</v>
+        <v>-0.1560465862355063</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04589325440145699</v>
+        <v>0.1647066940378106</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3417757628606957</v>
+        <v>0.9577975473342356</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2087,23 +2060,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds[T.True]</t>
+          <t>region_Europe[T.True]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1204114507205493</v>
+        <v>-0.05122561371632553</v>
       </c>
       <c r="C26" t="n">
-        <v>0.08544068728366003</v>
+        <v>0.1055959012379953</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04704921916977377</v>
+        <v>-0.2581897770578447</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2878721206108723</v>
+        <v>0.1557385496251937</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1587468589049512</v>
+        <v>0.6275984125035583</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2112,23 +2085,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Meets[T.True]</t>
+          <t>region_Latin_America[T.True]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.02051648839083488</v>
+        <v>-0.1108286684308806</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03958468775109256</v>
+        <v>0.1140937462761546</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.05706807394057035</v>
+        <v>-0.3344483019933944</v>
       </c>
       <c r="E27" t="n">
-        <v>0.09810105072224011</v>
+        <v>0.1127909651316332</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6042534715722546</v>
+        <v>0.3313578400077078</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2137,23 +2110,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Europe[T.True]</t>
+          <t>region_Middle_East_and_Africa[T.True]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.04589063008228283</v>
+        <v>-0.01220396724800446</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1072098662686151</v>
+        <v>0.1180185229028869</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.256018106756124</v>
+        <v>-0.2435160216462784</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1642368465915583</v>
+        <v>0.2191080871502694</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6686184746717895</v>
+        <v>0.9176397829023973</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2162,23 +2135,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Latin_America[T.True]</t>
+          <t>region_North_America[T.True]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1033298338839563</v>
+        <v>0.09048136114066323</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1144514749890517</v>
+        <v>0.1120837691629425</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3276506028399844</v>
+        <v>-0.1291987896702051</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1209909350720718</v>
+        <v>0.3101615119515316</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3666179412261609</v>
+        <v>0.4195135299990498</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2187,23 +2160,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa[T.True]</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.001087627169794378</v>
+        <v>-0.04579550992862588</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1154178290244132</v>
+        <v>0.0390974269238337</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2273024152314459</v>
+        <v>-0.1224250585875266</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2251271608918571</v>
+        <v>0.03083403873027481</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9924813342037202</v>
+        <v>0.2414710814149033</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_North_America[T.True]</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.09414803060478853</v>
+        <v>-0.0009841142683511377</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1107187689161672</v>
+        <v>0.005676324387152102</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.122856768883512</v>
+        <v>-0.01210950563173565</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3111528300930891</v>
+        <v>0.01014127709503338</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3951389319733076</v>
+        <v>0.8623592324210241</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2237,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0462805685330589</v>
+        <v>-0.009996935471112991</v>
       </c>
       <c r="C32" t="n">
-        <v>0.03888357660028012</v>
+        <v>0.006231431833130104</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.1224909782597123</v>
+        <v>-0.0222103174361644</v>
       </c>
       <c r="E32" t="n">
-        <v>0.02992984119359454</v>
+        <v>0.00221644649393842</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2339542956047752</v>
+        <v>0.1086532664978456</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2262,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.01848929803341687</v>
+        <v>-0.02241147003507639</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01553613538789587</v>
+        <v>0.01594802218291595</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.04893956385263101</v>
+        <v>-0.0536690191382375</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01196096778579727</v>
+        <v>0.008846079068084715</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2340135834927808</v>
+        <v>0.1599374102620117</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2287,23 +2260,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.01027709537380881</v>
+        <v>0.4536514594486488</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006207525280663823</v>
+        <v>0.0363354327751863</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.02244362135703179</v>
+        <v>0.3824353198466073</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00188943060941418</v>
+        <v>0.5248675990506901</v>
       </c>
       <c r="F34" t="n">
-        <v>0.09780557546747547</v>
+        <v>9.003178021304643e-36</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0009242342881632074</v>
+        <v>-0.01832790500755672</v>
       </c>
       <c r="C35" t="n">
-        <v>0.005862642636446789</v>
+        <v>0.07641092741851577</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.01241480270982786</v>
+        <v>-0.1680905707731518</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01056633413350145</v>
+        <v>0.1314347607580383</v>
       </c>
       <c r="F35" t="n">
-        <v>0.874734123929793</v>
+        <v>0.8104389944348604</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2337,50 +2310,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.01470820229201362</v>
+        <v>0.005570573422178937</v>
       </c>
       <c r="C36" t="n">
-        <v>0.07687161729689795</v>
+        <v>0.005006598757322851</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1653738036272799</v>
+        <v>-0.004242179827216841</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1359573990432526</v>
+        <v>0.01538332667157472</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8482634330645449</v>
+        <v>0.2658603809065231</v>
       </c>
       <c r="G36" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>baseline_workload</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0.4605018096450158</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.03712879248431222</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.3877307135863024</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.5332729057037292</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2.52279145028264e-35</v>
-      </c>
-      <c r="G37" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -2395,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2427,10 +2375,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-28.63902089506874</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+        <v>-2.680600179802938</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.4771933030981325</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.938181768271168e-08</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2439,13 +2391,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02313926327038869</v>
+        <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09767080877239748</v>
+        <v>0.1002143663033997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8127260403169279</v>
+        <v>0.79975540801217</v>
       </c>
     </row>
     <row r="4">
@@ -2455,13 +2407,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2234052412627341</v>
+        <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2328794784675677</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3373990767846601</v>
+        <v>0.3364439424069159</v>
       </c>
     </row>
     <row r="5">
@@ -2471,13 +2423,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8180627404127788</v>
+        <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.168995369134968</v>
+        <v>0.1734026513921177</v>
       </c>
       <c r="D5" t="n">
-        <v>1.293561512468184e-06</v>
+        <v>2.563995828054277e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2487,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03544498749501269</v>
+        <v>0.03527526670387295</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1931765748363377</v>
+        <v>0.191688294691954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8544175536043231</v>
+        <v>0.853994545471355</v>
       </c>
     </row>
     <row r="7">
@@ -2503,13 +2455,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2759060224168001</v>
+        <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1812662636985352</v>
+        <v>0.1901447102133382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1279831380955545</v>
+        <v>0.1446466431125516</v>
       </c>
     </row>
     <row r="8">
@@ -2519,13 +2471,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1078851505725079</v>
+        <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1932040224873154</v>
+        <v>0.1952515666982443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5765711865505436</v>
+        <v>0.5954095400432464</v>
       </c>
     </row>
     <row r="9">
@@ -2535,13 +2487,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8717785708706234</v>
+        <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1678649184861324</v>
+        <v>0.1695280942409136</v>
       </c>
       <c r="D9" t="n">
-        <v>2.065612399360983e-07</v>
+        <v>2.539495077342701e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2551,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.03735224036769266</v>
+        <v>-0.04456520772617086</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2698916793365708</v>
+        <v>0.2604021031716313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8899265459788944</v>
+        <v>0.8641137091517834</v>
       </c>
     </row>
     <row r="11">
@@ -2567,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.27139852374157</v>
+        <v>-0.2737623724798149</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2816070636601529</v>
+        <v>0.2787881385465057</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3351717854029546</v>
+        <v>0.3261132423877617</v>
       </c>
     </row>
     <row r="12">
@@ -2583,13 +2535,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08472740319915269</v>
+        <v>0.08100487957118127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2580923618181321</v>
+        <v>0.2596429772097166</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7426974963062474</v>
+        <v>0.7550514391424692</v>
       </c>
     </row>
     <row r="13">
@@ -2599,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0406830151843166</v>
+        <v>0.03917827337461736</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2611004769215555</v>
+        <v>0.2572958805743769</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8761799203818157</v>
+        <v>0.8789745077123745</v>
       </c>
     </row>
     <row r="14">
@@ -2615,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.0534569388448658</v>
+        <v>-0.05296103812307947</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2638638595233255</v>
+        <v>0.2610089865588713</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8394532566768507</v>
+        <v>0.8392062624375523</v>
       </c>
     </row>
     <row r="15">
@@ -2631,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1239335042278707</v>
+        <v>0.1181322726534159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2599280592390572</v>
+        <v>0.2572294350577177</v>
       </c>
       <c r="D15" t="n">
-        <v>0.633505078402905</v>
+        <v>0.646055612898408</v>
       </c>
     </row>
     <row r="16">
@@ -2647,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.001862882312047092</v>
+        <v>-0.004000986240379581</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2575901874165238</v>
+        <v>0.2383903410311186</v>
       </c>
       <c r="D16" t="n">
-        <v>0.994229779892155</v>
+        <v>0.9866094604655129</v>
       </c>
     </row>
     <row r="17">
@@ -2663,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1116424378427602</v>
+        <v>0.1057185310395304</v>
       </c>
       <c r="C17" t="n">
-        <v>0.258655496780073</v>
+        <v>0.2543340222421748</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6660132573861222</v>
+        <v>0.6776529122567303</v>
       </c>
     </row>
     <row r="18">
@@ -2679,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1317171712347951</v>
+        <v>-0.1377694895733256</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2668604742478565</v>
+        <v>0.2636874203313626</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6216023562146854</v>
+        <v>0.6013412201546261</v>
       </c>
     </row>
     <row r="19">
@@ -2695,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02274331928771129</v>
+        <v>-0.02557154094223238</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2635260646471042</v>
+        <v>0.252759790153811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.931224861952453</v>
+        <v>0.9194160355966675</v>
       </c>
     </row>
     <row r="20">
@@ -2711,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06665392434454051</v>
+        <v>-0.07344622569376427</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2656595207910754</v>
+        <v>0.267457860954101</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8018915682473747</v>
+        <v>0.7836169672222772</v>
       </c>
     </row>
     <row r="21">
@@ -2727,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.209601896539733</v>
+        <v>0.2063167170305059</v>
       </c>
       <c r="C21" t="n">
-        <v>0.248589943238082</v>
+        <v>0.244289653245072</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3991371664160996</v>
+        <v>0.3983578134719846</v>
       </c>
     </row>
     <row r="22">
@@ -2743,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1668969509213569</v>
+        <v>-0.1704634573362026</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2747515022959944</v>
+        <v>0.2696748454965904</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5435543655447144</v>
+        <v>0.5273167196806361</v>
       </c>
     </row>
     <row r="23">
@@ -2759,189 +2711,189 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4971940641809904</v>
+        <v>-0.5008110927334757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2924423487833311</v>
+        <v>0.287067218044571</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0891038687082271</v>
+        <v>0.08105838975171785</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>performance_rating_Exceeds[T.True]</t>
+          <t>performance_rating_Far_Exceeds[T.True]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26.21442552889307</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+        <v>0.9366864721074267</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1483430409733375</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.713396260923891e-10</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Below[T.True]</t>
+          <t>performance_rating_Meets[T.True]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.05451611819325158</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+        <v>-0.5776106069409677</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1143619392421807</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4.401383208103943e-07</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds[T.True]</t>
+          <t>region_Europe[T.True]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.15437389964459</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+        <v>0.237316144844174</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1503781926377478</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1145360411757813</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>performance_rating_Meets[T.True]</t>
+          <t>region_Latin_America[T.True]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25.63696707854778</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+        <v>-0.04350476117998651</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1611879340386412</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.7872365295400213</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>region_Europe[T.True]</t>
+          <t>region_Middle_East_and_Africa[T.True]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2375989005820465</v>
+        <v>-0.07514354096975732</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1483942012831661</v>
+        <v>0.1613683918223567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1093473930477332</v>
+        <v>0.6414556246120151</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Latin_America[T.True]</t>
+          <t>region_North_America[T.True]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.04390400011936763</v>
+        <v>0.09749293462742097</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1581709974633308</v>
+        <v>0.1543265796290165</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7813401518904401</v>
+        <v>0.5275624553510008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa[T.True]</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.07706864556783545</v>
+        <v>-0.002418133412192873</v>
       </c>
       <c r="C30" t="n">
-        <v>0.157805034131052</v>
+        <v>0.007135781003458546</v>
       </c>
       <c r="D30" t="n">
-        <v>0.625281499853628</v>
+        <v>0.7347043603418277</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_North_America[T.True]</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.09735884295380272</v>
+        <v>-0.005012017390962195</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1528329758431298</v>
+        <v>0.008304876992455039</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5241067842931748</v>
+        <v>0.5461741835341576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.02140998846971486</v>
+        <v>-0.004129656026475419</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02125751820943617</v>
+        <v>0.02222260881033174</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3138518697695356</v>
+        <v>0.8525770672961279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004963851467076696</v>
+        <v>0.2280638724458785</v>
       </c>
       <c r="C33" t="n">
-        <v>0.008295015527601023</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5495638837808257</v>
+        <v>0.04668969945129923</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.002369150025833512</v>
+        <v>0.006335499136474495</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007250684388762908</v>
+        <v>0.006871422968197181</v>
       </c>
       <c r="D34" t="n">
-        <v>0.7438581373216515</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>is_new_manager</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0.2289921174550882</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.1106079911199388</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0.03842392670154298</v>
+        <v>0.3565249957666435</v>
       </c>
     </row>
   </sheetData>
